--- a/renommage-entete-FHIR/ig/StructureDefinition-fr-lm-evenement.xlsx
+++ b/renommage-entete-FHIR/ig/StructureDefinition-fr-lm-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T21:31:34+00:00</t>
+    <t>2025-10-21T21:35:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/renommage-entete-FHIR/ig/StructureDefinition-fr-lm-evenement.xlsx
+++ b/renommage-entete-FHIR/ig/StructureDefinition-fr-lm-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T21:35:58+00:00</t>
+    <t>2025-10-21T22:51:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/renommage-entete-FHIR/ig/StructureDefinition-fr-lm-evenement.xlsx
+++ b/renommage-entete-FHIR/ig/StructureDefinition-fr-lm-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T22:51:41+00:00</t>
+    <t>2025-10-21T23:32:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
